--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price</t>
         </is>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,22 +429,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -451,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>33.66096741140925</v>
+        <v>28.76311685796437</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.57198587734609</v>
+        <v>26.67812243022348</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.75215364326838</v>
+        <v>20.29933862386613</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.35318552095479</v>
+        <v>25.88437475695901</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.31997850129211</v>
+        <v>28.42436158257655</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>24.25965044857275</v>
+        <v>30.3070305647596</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -463,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.76311685796437</v>
+        <v>22.95376288445232</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26.67812243022348</v>
+        <v>33.11141005628575</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.29933862386613</v>
+        <v>26.85360736787745</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25.88437475695901</v>
+        <v>27.77088076774225</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.42436158257655</v>
+        <v>28.26210325294796</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30.3070305647596</v>
+        <v>27.54093855066132</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.95376288445232</v>
+        <v>28.3109715068611</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.11141005628575</v>
+        <v>27.30185493356759</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26.85360736787745</v>
+        <v>27.13124490525066</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27.77088076774225</v>
+        <v>30.77083376118918</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.26210325294796</v>
+        <v>32.74138707845071</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27.54093855066132</v>
+        <v>23.9003550783252</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.3109715068611</v>
+        <v>33.66096741140925</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.30185493356759</v>
+        <v>29.57198587734609</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.13124490525066</v>
+        <v>23.75215364326838</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.77083376118918</v>
+        <v>29.35318552095479</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.74138707845071</v>
+        <v>28.31997850129211</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23.9003550783252</v>
+        <v>24.25965044857275</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>33.66096741140925</v>
+        <v>28.3109715068611</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.57198587734609</v>
+        <v>27.30185493356759</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.75215364326838</v>
+        <v>27.13124490525066</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.35318552095479</v>
+        <v>30.77083376118918</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.31997850129211</v>
+        <v>32.74138707845071</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>24.25965044857275</v>
+        <v>23.9003550783252</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,22 +429,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -451,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.3109715068611</v>
+        <v>33.66096741140925</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.30185493356759</v>
+        <v>29.57198587734609</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.13124490525066</v>
+        <v>23.75215364326838</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.77083376118918</v>
+        <v>29.35318552095479</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.74138707845071</v>
+        <v>28.31997850129211</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23.9003550783252</v>
+        <v>24.25965044857275</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>33.66096741140925</v>
+        <v>33.95013896447797</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.57198587734609</v>
+        <v>25.76927111328914</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.75215364326838</v>
+        <v>27.55313948397267</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.35318552095479</v>
+        <v>27.00147324216813</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.31997850129211</v>
+        <v>34.3270320893449</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>24.25965044857275</v>
+        <v>17.80774000699306</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios111.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -463,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>33.95013896447797</v>
+        <v>24.67272263443415</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.76927111328914</v>
+        <v>26.81393525361962</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.55313948397267</v>
+        <v>25.51816790450784</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27.00147324216813</v>
+        <v>26.29854720007824</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>34.3270320893449</v>
+        <v>32.39992236862933</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.80774000699306</v>
+        <v>32.49114292663671</v>
       </c>
     </row>
   </sheetData>
